--- a/outputs/churn_list.xlsx
+++ b/outputs/churn_list.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="churn_scoring" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="churn_scoring" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -603,7 +603,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="J4" t="n">
-        <v>0.8760978589587833</v>
+        <v>0.8760978589587832</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         <v>8.699999999999999</v>
       </c>
       <c r="J19" t="n">
-        <v>0.8659364916932292</v>
+        <v>0.8659364916932289</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>8.6</v>
       </c>
       <c r="J23" t="n">
-        <v>0.8631895254941483</v>
+        <v>0.863189525494148</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
         <v>8.6</v>
       </c>
       <c r="J24" t="n">
-        <v>0.8627400104077491</v>
+        <v>0.8627400104077489</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         <v>8.6</v>
       </c>
       <c r="J27" t="n">
-        <v>0.8613501262609682</v>
+        <v>0.8613501262609681</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -1845,7 +1845,7 @@
         <v>8.6</v>
       </c>
       <c r="J31" t="n">
-        <v>0.8605082414167943</v>
+        <v>0.8605082414167941</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         <v>8.6</v>
       </c>
       <c r="J33" t="n">
-        <v>0.8600289428213858</v>
+        <v>0.860028942821386</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -2489,7 +2489,7 @@
         <v>8.4</v>
       </c>
       <c r="J45" t="n">
-        <v>0.839165826692382</v>
+        <v>0.8391658266923819</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>8.1</v>
       </c>
       <c r="J52" t="n">
-        <v>0.8100313194807912</v>
+        <v>0.8100313194807911</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
@@ -6169,7 +6169,7 @@
         <v>1.6</v>
       </c>
       <c r="J125" t="n">
-        <v>0.1647706950266929</v>
+        <v>0.164770695026693</v>
       </c>
       <c r="K125" t="inlineStr">
         <is>
@@ -6445,7 +6445,7 @@
         <v>1.6</v>
       </c>
       <c r="J131" t="n">
-        <v>0.155371491068406</v>
+        <v>0.1553714910684061</v>
       </c>
       <c r="K131" t="inlineStr">
         <is>
@@ -6721,7 +6721,7 @@
         <v>1.5</v>
       </c>
       <c r="J137" t="n">
-        <v>0.1483407168641739</v>
+        <v>0.148340716864174</v>
       </c>
       <c r="K137" t="inlineStr">
         <is>
